--- a/data/trans_orig/P36B13_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B13_R-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32609</t>
+          <t>33140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31208</t>
+          <t>30029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54376</t>
+          <t>53237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69022</t>
+          <t>68074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106447</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232104</t>
+          <t>232843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>259565</t>
+          <t>259034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234327</t>
+          <t>235466</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257495</t>
+          <t>258674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>474430</t>
+          <t>477032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>511855</t>
+          <t>512803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54486</t>
+          <t>52219</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84729</t>
+          <t>83369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53442</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88838</t>
+          <t>89730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125979</t>
+          <t>128858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417846</t>
+          <t>419206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448089</t>
+          <t>450356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468295</t>
+          <t>469374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492848</t>
+          <t>492971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>898333</t>
+          <t>895454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935474</t>
+          <t>934582</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,24%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47895</t>
+          <t>47036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74893</t>
+          <t>72742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>24625</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46256</t>
+          <t>45719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79185</t>
+          <t>79783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115282</t>
+          <t>115268</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>240746</t>
+          <t>242897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267744</t>
+          <t>268603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290053</t>
+          <t>290590</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312271</t>
+          <t>311684</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>536666</t>
+          <t>536680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>572763</t>
+          <t>572165</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>34619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60271</t>
+          <t>60345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13686</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34366</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53630</t>
+          <t>53554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86875</t>
+          <t>85887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308795</t>
+          <t>308721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334813</t>
+          <t>334447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348515</t>
+          <t>349781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369195</t>
+          <t>368749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665072</t>
+          <t>666060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>698317</t>
+          <t>698393</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41851</t>
+          <t>41731</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181407</t>
+          <t>180268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198173</t>
+          <t>197833</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199873</t>
+          <t>198719</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212316</t>
+          <t>212320</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>385982</t>
+          <t>386102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407022</t>
+          <t>406715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25734</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16752</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17378</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36443</t>
+          <t>36355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237389</t>
+          <t>238141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253469</t>
+          <t>253333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256363</t>
+          <t>256928</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268837</t>
+          <t>269259</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>499795</t>
+          <t>499883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518860</t>
+          <t>519687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41762</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72650</t>
+          <t>71607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25248</t>
+          <t>25718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48932</t>
+          <t>48362</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72509</t>
+          <t>74394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110022</t>
+          <t>112420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>570825</t>
+          <t>571868</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>601998</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>631329</t>
+          <t>631899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>655013</t>
+          <t>654543</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1213715</t>
+          <t>1211317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1251228</t>
+          <t>1249343</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91745</t>
+          <t>90864</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129705</t>
+          <t>129180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67931</t>
+          <t>68849</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105582</t>
+          <t>105029</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>168074</t>
+          <t>170356</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222141</t>
+          <t>221777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>647852</t>
+          <t>648377</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>685812</t>
+          <t>686693</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>714879</t>
+          <t>715432</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>752530</t>
+          <t>751612</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1375877</t>
+          <t>1376241</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1429944</t>
+          <t>1427662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>383818</t>
+          <t>385296</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>460533</t>
+          <t>460979</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>247534</t>
+          <t>246674</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>310290</t>
+          <t>307483</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>651834</t>
+          <t>647309</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>748461</t>
+          <t>745995</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2913232</t>
+          <t>2912786</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2989947</t>
+          <t>2988469</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3210856</t>
+          <t>3213663</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3273612</t>
+          <t>3274472</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6146450</t>
+          <t>6148916</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6243077</t>
+          <t>6247602</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4197,27 +4197,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>288069</t>
+          <t>314973</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280756</t>
+          <t>310688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4232,27 +4232,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>599511</t>
+          <t>633818</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592203</t>
+          <t>628158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38570</t>
+          <t>37093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20597</t>
+          <t>21344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32519</t>
+          <t>33136</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19546</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50427</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>498267</t>
+          <t>510182</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479820</t>
+          <t>493554</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>507541</t>
+          <t>520194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>501186</t>
+          <t>532438</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492984</t>
+          <t>523765</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506428</t>
+          <t>537966</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>999452</t>
+          <t>1042620</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>981544</t>
+          <t>1026592</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1012425</t>
+          <t>1054882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513581</t>
+          <t>545109</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513581</t>
+          <t>545109</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513581</t>
+          <t>545109</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031971</t>
+          <t>1075756</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031971</t>
+          <t>1075756</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031971</t>
+          <t>1075756</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>21420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4805,32 +4805,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>26798</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>37804</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>298501</t>
+          <t>299098</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288746</t>
+          <t>290491</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305402</t>
+          <t>305154</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>329220</t>
+          <t>336489</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321606</t>
+          <t>327669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335144</t>
+          <t>342139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>627722</t>
+          <t>635588</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616415</t>
+          <t>624582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636691</t>
+          <t>644629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>311904</t>
+          <t>311911</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>311904</t>
+          <t>311911</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>311904</t>
+          <t>311911</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>343138</t>
+          <t>350475</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>343138</t>
+          <t>350475</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>343138</t>
+          <t>350475</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>655042</t>
+          <t>662386</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>655042</t>
+          <t>662386</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>655042</t>
+          <t>662386</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5148,32 +5148,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21673</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39653</t>
+          <t>47228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>296736</t>
+          <t>350300</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282086</t>
+          <t>331595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305067</t>
+          <t>361062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>469866</t>
+          <t>414985</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>464732</t>
+          <t>409316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473308</t>
+          <t>418801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>766601</t>
+          <t>765285</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748621</t>
+          <t>747879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>775777</t>
+          <t>777301</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5421,32 +5421,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5456,32 +5456,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5491,32 +5491,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>9728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5534,32 +5534,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>175771</t>
+          <t>202407</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171998</t>
+          <t>198005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177612</t>
+          <t>204467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>206019</t>
+          <t>224498</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202847</t>
+          <t>221279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207189</t>
+          <t>225686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5604,32 +5604,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>381789</t>
+          <t>426905</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377680</t>
+          <t>422328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384287</t>
+          <t>429785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207860</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207860</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207860</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386601</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386601</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386601</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19138</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5834,32 +5834,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20373</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5877,32 +5877,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>260347</t>
+          <t>262140</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250498</t>
+          <t>253090</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265067</t>
+          <t>266901</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5912,27 +5912,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>255650</t>
+          <t>262332</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250078</t>
+          <t>256494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5947,32 +5947,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>515998</t>
+          <t>524471</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>506319</t>
+          <t>515410</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521397</t>
+          <t>529635</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>64822</t>
+          <t>70780</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46971</t>
+          <t>52708</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88894</t>
+          <t>94167</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6142,32 +6142,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30849</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>27008</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49007</t>
+          <t>53140</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>95671</t>
+          <t>109004</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>87688</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>127247</t>
+          <t>136476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -6220,32 +6220,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>559457</t>
+          <t>648907</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>535385</t>
+          <t>625520</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>577308</t>
+          <t>666979</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6255,32 +6255,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>816966</t>
+          <t>732257</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>798808</t>
+          <t>717341</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>834146</t>
+          <t>743473</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1376424</t>
+          <t>1381164</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1344848</t>
+          <t>1353692</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1412692</t>
+          <t>1402480</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847815</t>
+          <t>770481</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847815</t>
+          <t>770481</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847815</t>
+          <t>770481</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472095</t>
+          <t>1490168</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472095</t>
+          <t>1490168</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472095</t>
+          <t>1490168</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6450,32 +6450,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>350833</t>
+          <t>125049</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134955</t>
+          <t>101740</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>668561</t>
+          <t>151958</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6485,32 +6485,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>58491</t>
+          <t>68121</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46156</t>
+          <t>53104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75092</t>
+          <t>87088</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>409324</t>
+          <t>193170</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>185604</t>
+          <t>166487</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>874696</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -6563,32 +6563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>577887</t>
+          <t>673023</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>260159</t>
+          <t>646114</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>793765</t>
+          <t>696332</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6598,32 +6598,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>659240</t>
+          <t>763210</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>642639</t>
+          <t>744243</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>671575</t>
+          <t>778227</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1237128</t>
+          <t>1436233</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>771756</t>
+          <t>1406041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1460848</t>
+          <t>1462916</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>477261</t>
+          <t>263777</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>240232</t>
+          <t>226688</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1227438</t>
+          <t>307138</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>126318</t>
+          <t>144376</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>100023</t>
+          <t>121123</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>150946</t>
+          <t>169961</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6863,32 +6863,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>603580</t>
+          <t>408153</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>356457</t>
+          <t>364422</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1400988</t>
+          <t>459804</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -6906,32 +6906,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2978410</t>
+          <t>3264903</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2228233</t>
+          <t>3221542</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3215439</t>
+          <t>3301992</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3526216</t>
+          <t>3581184</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3501588</t>
+          <t>3555599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3552511</t>
+          <t>3604437</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6976,32 +6976,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6504624</t>
+          <t>6846087</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5707216</t>
+          <t>6794436</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6751747</t>
+          <t>6889818</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7019,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
